--- a/tests/output_file/indices_calculation.xlsx
+++ b/tests/output_file/indices_calculation.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,59 +417,59 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Sample</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Instability_Index</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Expansion_Index</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Allele_Ratio</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>LOI_CAA</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>LOI_CCA</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>DOI</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>CAG_repeatsPeak_Allele_1</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>CAG_repeatsPeak_Allele_2</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Max_CAG_observed</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" t="n">
         <v>0</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -518,7 +506,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" t="n">
         <v>1</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -555,7 +543,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" t="n">
         <v>2</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -592,7 +580,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" t="n">
         <v>3</v>
       </c>
       <c r="B5" t="inlineStr">

--- a/tests/output_file/indices_calculation.xlsx
+++ b/tests/output_file/indices_calculation.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -478,19 +478,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8.993377483443707</v>
+        <v>0.1777777777777778</v>
       </c>
       <c r="D2" t="n">
-        <v>91.13643178410794</v>
+        <v>10.66666666666667</v>
       </c>
       <c r="E2" t="n">
-        <v>0.24</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -499,10 +499,10 @@
         <v>16</v>
       </c>
       <c r="J2" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="K2" t="n">
-        <v>99</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
@@ -515,31 +515,31 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8.379971840901092</v>
+        <v>0.861111111111111</v>
       </c>
       <c r="D3" t="n">
-        <v>71.44878706199462</v>
+        <v>10.66666666666667</v>
       </c>
       <c r="E3" t="n">
-        <v>1.11</v>
+        <v>0.45</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H3" t="n">
-        <v>80</v>
+        <v>80.83333333333333</v>
       </c>
       <c r="I3" t="n">
         <v>17</v>
       </c>
       <c r="J3" t="n">
+        <v>30</v>
+      </c>
+      <c r="K3" t="n">
         <v>31</v>
-      </c>
-      <c r="K3" t="n">
-        <v>99</v>
       </c>
     </row>
     <row r="4">
@@ -548,23 +548,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>reduced_penetrance_17_38_LOICCA.fastq.gz</t>
+          <t>reduced_penetrance_17_37_LOICCA.fastq.gz</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7.327214400285154</v>
+        <v>0.975</v>
       </c>
       <c r="D4" t="n">
-        <v>57.39227895392279</v>
+        <v>39</v>
       </c>
       <c r="E4" t="n">
-        <v>1.28</v>
+        <v>0.48</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>2.173913043478261</v>
       </c>
       <c r="G4" t="n">
-        <v>75</v>
+        <v>73.91304347826086</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -573,10 +573,10 @@
         <v>18</v>
       </c>
       <c r="J4" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K4" t="n">
-        <v>99</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5">
@@ -585,35 +585,35 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>full_penetrance_22_48_LOI.fastq.gz</t>
+          <t>high_expansion_18_75_NOLOI.fastq.gz</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4.615384615384616</v>
+        <v>0.6875</v>
       </c>
       <c r="D5" t="n">
-        <v>44</v>
+        <v>8.666666666666666</v>
       </c>
       <c r="E5" t="n">
-        <v>1.29</v>
+        <v>0.67</v>
       </c>
       <c r="F5" t="n">
-        <v>72</v>
+        <v>4.516129032258064</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>6.451612903225806</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J5" t="n">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="K5" t="n">
-        <v>101</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
